--- a/pharmacy_forms/045_moderna_covid_19_vaccine_appointment_scheduling_and_consent_form_cpesn--pharmacy_forms.xlsx
+++ b/pharmacy_forms/045_moderna_covid_19_vaccine_appointment_scheduling_and_consent_form_cpesn--pharmacy_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
